--- a/artfynd/A 2837-2024 artfynd.xlsx
+++ b/artfynd/A 2837-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1654,6 +1654,1586 @@
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>114768336</v>
+      </c>
+      <c r="B11" t="n">
+        <v>57248</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Mörtviken (Mörtviken), Sm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>568620</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6380585</v>
+      </c>
+      <c r="S11" t="n">
+        <v>1</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Tuna</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2024-02-21</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2024-02-21</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Louise Lundberg</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Louise Lundberg</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>114768376</v>
+      </c>
+      <c r="B12" t="n">
+        <v>97532</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Mörtviken (Mörtviken), Sm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>568615</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6380587</v>
+      </c>
+      <c r="S12" t="n">
+        <v>1</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Tuna</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2024-02-21</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2024-02-21</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Louise Lundberg</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Louise Lundberg</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>114788030</v>
+      </c>
+      <c r="B13" t="n">
+        <v>94316</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>2180</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Blåmossa</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Leucobryum glaucum</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Mörtviken, Sm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>568904</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6380491</v>
+      </c>
+      <c r="S13" t="n">
+        <v>25</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Tuna</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2024-02-22</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2024-02-22</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>114785740</v>
+      </c>
+      <c r="B14" t="n">
+        <v>96494</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Mörtviken, Sm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>568718</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6380688</v>
+      </c>
+      <c r="S14" t="n">
+        <v>25</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Tuna</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2024-02-22</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2024-02-22</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>114787955</v>
+      </c>
+      <c r="B15" t="n">
+        <v>94316</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>2180</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Blåmossa</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Leucobryum glaucum</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Mörtviken, Sm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>568950</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6380508</v>
+      </c>
+      <c r="S15" t="n">
+        <v>25</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Tuna</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2024-02-22</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2024-02-22</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>114786559</v>
+      </c>
+      <c r="B16" t="n">
+        <v>57251</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Mörtviken, Sm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>568886</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6380659</v>
+      </c>
+      <c r="S16" t="n">
+        <v>25</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Tuna</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2024-02-22</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2024-02-22</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>114786650</v>
+      </c>
+      <c r="B17" t="n">
+        <v>91503</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Mörtviken, Sm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>568925</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6380647</v>
+      </c>
+      <c r="S17" t="n">
+        <v>25</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Tuna</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2024-02-22</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2024-02-22</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>114785684</v>
+      </c>
+      <c r="B18" t="n">
+        <v>90257</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Mörtviken, Sm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>568636</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6380709</v>
+      </c>
+      <c r="S18" t="n">
+        <v>25</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Tuna</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2024-02-22</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2024-02-22</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>114786986</v>
+      </c>
+      <c r="B19" t="n">
+        <v>97535</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Mörtviken, Sm</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>569098</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6380659</v>
+      </c>
+      <c r="S19" t="n">
+        <v>25</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Tuna</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2024-02-22</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2024-02-22</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>114786336</v>
+      </c>
+      <c r="B20" t="n">
+        <v>97535</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Mörtviken, Sm</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>568618</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6380592</v>
+      </c>
+      <c r="S20" t="n">
+        <v>25</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Tuna</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2024-02-22</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2024-02-22</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>114788690</v>
+      </c>
+      <c r="B21" t="n">
+        <v>97535</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Mörtviken, Sm</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>568826</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6380586</v>
+      </c>
+      <c r="S21" t="n">
+        <v>25</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Tuna</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2024-02-22</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2024-02-22</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>114788800</v>
+      </c>
+      <c r="B22" t="n">
+        <v>97535</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Mörtviken, Sm</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>568781</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6380607</v>
+      </c>
+      <c r="S22" t="n">
+        <v>25</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Tuna</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2024-02-22</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2024-02-22</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>114787547</v>
+      </c>
+      <c r="B23" t="n">
+        <v>90260</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Mörtviken, Sm</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>569069</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6380752</v>
+      </c>
+      <c r="S23" t="n">
+        <v>25</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Tuna</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2024-02-22</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2024-02-22</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>114785524</v>
+      </c>
+      <c r="B24" t="n">
+        <v>94313</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>2180</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Blåmossa</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Leucobryum glaucum</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Mörtviken, Sm</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>568607</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6380751</v>
+      </c>
+      <c r="S24" t="n">
+        <v>25</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Tuna</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2024-02-22</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2024-02-22</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>114787226</v>
+      </c>
+      <c r="B25" t="n">
+        <v>57251</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Mörtviken, Sm</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>569134</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6380784</v>
+      </c>
+      <c r="S25" t="n">
+        <v>25</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Tuna</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2024-02-22</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2024-02-22</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 2837-2024 artfynd.xlsx
+++ b/artfynd/A 2837-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY25"/>
+  <dimension ref="A1:AY45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3234,6 +3234,2298 @@
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>114799643</v>
+      </c>
+      <c r="B26" t="n">
+        <v>97535</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>A 2837, Tunasjön, Sm</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>569137</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6380687</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Tuna</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2024-02-22</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2024-02-22</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF26" t="inlineStr"/>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>114799431</v>
+      </c>
+      <c r="B27" t="n">
+        <v>97535</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>A 2837, Tunasjön, Sm</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>568951</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6380627</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Tuna</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2024-02-22</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2024-02-22</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF27" t="inlineStr"/>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>114799394</v>
+      </c>
+      <c r="B28" t="n">
+        <v>97535</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>A 2837, Tunasjön, Sm</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>568951</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6380559</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Tuna</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2024-02-22</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2024-02-22</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF28" t="inlineStr"/>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>114799740</v>
+      </c>
+      <c r="B29" t="n">
+        <v>57251</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>A 2837, Tunasjön, Sm</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>568635</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6380643</v>
+      </c>
+      <c r="S29" t="n">
+        <v>100</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Tuna</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2024-02-22</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2024-02-22</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>114799449</v>
+      </c>
+      <c r="B30" t="n">
+        <v>97535</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>A 2837, Tunasjön, Sm</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>568965</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6380609</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Tuna</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2024-02-22</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2024-02-22</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF30" t="inlineStr"/>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>114799506</v>
+      </c>
+      <c r="B31" t="n">
+        <v>97535</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>A 2837, Tunasjön, Sm</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>569040</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6380719</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Tuna</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2024-02-22</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2024-02-22</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF31" t="inlineStr"/>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>114799476</v>
+      </c>
+      <c r="B32" t="n">
+        <v>57384</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>A 2837, Tunasjön, Sm</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>569029</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6380721</v>
+      </c>
+      <c r="S32" t="n">
+        <v>25</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Tuna</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2024-02-22</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2024-02-22</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>114799611</v>
+      </c>
+      <c r="B33" t="n">
+        <v>97535</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>A 2837, Tunasjön, Sm</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>569117</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6380691</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Tuna</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2024-02-22</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2024-02-22</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF33" t="inlineStr"/>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>114799596</v>
+      </c>
+      <c r="B34" t="n">
+        <v>97535</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>A 2837, Tunasjön, Sm</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>569109</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6380682</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Tuna</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2024-02-22</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2024-02-22</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF34" t="inlineStr"/>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>114799704</v>
+      </c>
+      <c r="B35" t="n">
+        <v>97535</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>A 2837, Tunasjön, Sm</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>568645</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6380578</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Tuna</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2024-02-22</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2024-02-22</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF35" t="inlineStr"/>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>114799660</v>
+      </c>
+      <c r="B36" t="n">
+        <v>97535</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>A 2837, Tunasjön, Sm</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>569155</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6380762</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Tuna</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2024-02-22</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2024-02-22</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF36" t="inlineStr"/>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>114799627</v>
+      </c>
+      <c r="B37" t="n">
+        <v>97535</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>A 2837, Tunasjön, Sm</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>569112</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6380686</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Tuna</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2024-02-22</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2024-02-22</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF37" t="inlineStr"/>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>114799410</v>
+      </c>
+      <c r="B38" t="n">
+        <v>97535</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>A 2837, Tunasjön, Sm</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>568959</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6380594</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Tuna</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2024-02-22</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2024-02-22</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF38" t="inlineStr"/>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>114799529</v>
+      </c>
+      <c r="B39" t="n">
+        <v>97535</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>A 2837, Tunasjön, Sm</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>569144</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6380753</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Tuna</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2024-02-22</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2024-02-22</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF39" t="inlineStr"/>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>114799722</v>
+      </c>
+      <c r="B40" t="n">
+        <v>57251</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>A 2837, Tunasjön, Sm</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>568601</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6380587</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Tuna</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2024-02-22</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2024-02-22</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>114799683</v>
+      </c>
+      <c r="B41" t="n">
+        <v>57384</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>A 2837, Tunasjön, Sm</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>568842</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6380500</v>
+      </c>
+      <c r="S41" t="n">
+        <v>25</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Tuna</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2024-02-22</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2024-02-22</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>114799582</v>
+      </c>
+      <c r="B42" t="n">
+        <v>97535</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>A 2837, Tunasjön, Sm</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>569082</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6380654</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Tuna</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2024-02-22</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2024-02-22</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF42" t="inlineStr"/>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>114799539</v>
+      </c>
+      <c r="B43" t="n">
+        <v>97535</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>A 2837, Tunasjön, Sm</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>569136</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6380752</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Tuna</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2024-02-22</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2024-02-22</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF43" t="inlineStr"/>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>114799755</v>
+      </c>
+      <c r="B44" t="n">
+        <v>97535</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>A 2837, Tunasjön, Sm</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>568732</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6380593</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Tuna</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2024-02-22</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2024-02-22</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF44" t="inlineStr"/>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>114799466</v>
+      </c>
+      <c r="B45" t="n">
+        <v>97535</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>A 2837, Tunasjön, Sm</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>568997</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6380645</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Tuna</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2024-02-22</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2024-02-22</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF45" t="inlineStr"/>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 2837-2024 artfynd.xlsx
+++ b/artfynd/A 2837-2024 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 2837-2024 artfynd.xlsx
+++ b/artfynd/A 2837-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY45"/>
+  <dimension ref="A1:AY48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1871,10 +1871,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>114788030</v>
+        <v>114766795</v>
       </c>
       <c r="B13" t="n">
-        <v>94316</v>
+        <v>57597</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1887,38 +1887,38 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2180</v>
+        <v>103015</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Mörtviken, Sm</t>
+          <t>Fallebo (Fallebo), Sm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>568904</v>
+        <v>568885</v>
       </c>
       <c r="R13" t="n">
-        <v>6380491</v>
+        <v>6380519</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2024-02-22</t>
+          <t>2024-02-21</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2024-02-22</t>
+          <t>2024-02-21</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1962,22 +1962,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>114785740</v>
+        <v>114788030</v>
       </c>
       <c r="B14" t="n">
-        <v>96494</v>
+        <v>94316</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1990,21 +1990,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221945</v>
+        <v>2180</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2015,10 +2015,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>568718</v>
+        <v>568904</v>
       </c>
       <c r="R14" t="n">
-        <v>6380688</v>
+        <v>6380491</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2077,10 +2077,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>114787955</v>
+        <v>114785740</v>
       </c>
       <c r="B15" t="n">
-        <v>94316</v>
+        <v>96494</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2093,21 +2093,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2180</v>
+        <v>221945</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2118,10 +2118,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>568950</v>
+        <v>568718</v>
       </c>
       <c r="R15" t="n">
-        <v>6380508</v>
+        <v>6380688</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2180,10 +2180,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>114786559</v>
+        <v>114787955</v>
       </c>
       <c r="B16" t="n">
-        <v>57251</v>
+        <v>94316</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2192,25 +2192,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2221,10 +2221,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>568886</v>
+        <v>568950</v>
       </c>
       <c r="R16" t="n">
-        <v>6380659</v>
+        <v>6380508</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2257,11 +2257,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2024-02-22</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2288,10 +2283,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>114786650</v>
+        <v>114786559</v>
       </c>
       <c r="B17" t="n">
-        <v>91503</v>
+        <v>57251</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2300,25 +2295,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2329,10 +2324,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>568925</v>
+        <v>568886</v>
       </c>
       <c r="R17" t="n">
-        <v>6380647</v>
+        <v>6380659</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2365,6 +2360,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-02-22</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2391,10 +2391,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>114785684</v>
+        <v>114786650</v>
       </c>
       <c r="B18" t="n">
-        <v>90257</v>
+        <v>91503</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2403,25 +2403,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5442</v>
+        <v>4364</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2432,10 +2432,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>568636</v>
+        <v>568925</v>
       </c>
       <c r="R18" t="n">
-        <v>6380709</v>
+        <v>6380647</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2494,10 +2494,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>114786986</v>
+        <v>114785684</v>
       </c>
       <c r="B19" t="n">
-        <v>97535</v>
+        <v>90257</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2506,32 +2506,28 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2539,10 +2535,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>569098</v>
+        <v>568636</v>
       </c>
       <c r="R19" t="n">
-        <v>6380659</v>
+        <v>6380709</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2601,7 +2597,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>114786336</v>
+        <v>114786986</v>
       </c>
       <c r="B20" t="n">
         <v>97535</v>
@@ -2636,7 +2632,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>50</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
@@ -2646,10 +2642,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>568618</v>
+        <v>569098</v>
       </c>
       <c r="R20" t="n">
-        <v>6380592</v>
+        <v>6380659</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2708,7 +2704,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>114788690</v>
+        <v>114786336</v>
       </c>
       <c r="B21" t="n">
         <v>97535</v>
@@ -2743,7 +2739,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
@@ -2753,10 +2749,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>568826</v>
+        <v>568618</v>
       </c>
       <c r="R21" t="n">
-        <v>6380586</v>
+        <v>6380592</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2815,7 +2811,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>114788800</v>
+        <v>114788690</v>
       </c>
       <c r="B22" t="n">
         <v>97535</v>
@@ -2850,7 +2846,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>5</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
@@ -2860,10 +2856,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>568781</v>
+        <v>568826</v>
       </c>
       <c r="R22" t="n">
-        <v>6380607</v>
+        <v>6380586</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2922,10 +2918,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>114787547</v>
+        <v>114788800</v>
       </c>
       <c r="B23" t="n">
-        <v>90260</v>
+        <v>97535</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2934,28 +2930,32 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="K23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -2963,10 +2963,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>569069</v>
+        <v>568781</v>
       </c>
       <c r="R23" t="n">
-        <v>6380752</v>
+        <v>6380607</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3025,10 +3025,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>114785524</v>
+        <v>114787547</v>
       </c>
       <c r="B24" t="n">
-        <v>94313</v>
+        <v>90260</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3037,25 +3037,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2180</v>
+        <v>5442</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3066,10 +3066,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>568607</v>
+        <v>569069</v>
       </c>
       <c r="R24" t="n">
-        <v>6380751</v>
+        <v>6380752</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3128,10 +3128,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>114787226</v>
+        <v>114785524</v>
       </c>
       <c r="B25" t="n">
-        <v>57251</v>
+        <v>94313</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3140,25 +3140,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3169,10 +3169,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>569134</v>
+        <v>568607</v>
       </c>
       <c r="R25" t="n">
-        <v>6380784</v>
+        <v>6380751</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3205,11 +3205,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2024-02-22</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3236,10 +3231,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>114799643</v>
+        <v>114787226</v>
       </c>
       <c r="B26" t="n">
-        <v>97535</v>
+        <v>57251</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3248,53 +3243,42 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>A 2837, Tunasjön, Sm</t>
+          <t>Mörtviken, Sm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>569137</v>
+        <v>569134</v>
       </c>
       <c r="R26" t="n">
-        <v>6380687</v>
+        <v>6380784</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3326,32 +3310,36 @@
           <t>2024-02-22</t>
         </is>
       </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
+        </is>
+      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>114799431</v>
+        <v>114799643</v>
       </c>
       <c r="B27" t="n">
         <v>97535</v>
@@ -3386,7 +3374,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -3403,10 +3391,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>568951</v>
+        <v>569137</v>
       </c>
       <c r="R27" t="n">
-        <v>6380627</v>
+        <v>6380687</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3466,7 +3454,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>114799394</v>
+        <v>114799431</v>
       </c>
       <c r="B28" t="n">
         <v>97535</v>
@@ -3501,7 +3489,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -3521,7 +3509,7 @@
         <v>568951</v>
       </c>
       <c r="R28" t="n">
-        <v>6380559</v>
+        <v>6380627</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3581,10 +3569,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>114799740</v>
+        <v>114799394</v>
       </c>
       <c r="B29" t="n">
-        <v>57251</v>
+        <v>97535</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3593,39 +3581,39 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3633,13 +3621,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>568635</v>
+        <v>568951</v>
       </c>
       <c r="R29" t="n">
-        <v>6380643</v>
+        <v>6380559</v>
       </c>
       <c r="S29" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3677,6 +3665,7 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3695,10 +3684,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>114799449</v>
+        <v>114799740</v>
       </c>
       <c r="B30" t="n">
-        <v>97535</v>
+        <v>57251</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3707,39 +3696,39 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3747,13 +3736,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>568965</v>
+        <v>568635</v>
       </c>
       <c r="R30" t="n">
-        <v>6380609</v>
+        <v>6380643</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3791,7 +3780,6 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3810,7 +3798,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>114799506</v>
+        <v>114799449</v>
       </c>
       <c r="B31" t="n">
         <v>97535</v>
@@ -3862,10 +3850,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>569040</v>
+        <v>568965</v>
       </c>
       <c r="R31" t="n">
-        <v>6380719</v>
+        <v>6380609</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3925,10 +3913,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>114799476</v>
+        <v>114799506</v>
       </c>
       <c r="B32" t="n">
-        <v>57384</v>
+        <v>97535</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3937,39 +3925,39 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -3977,13 +3965,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>569029</v>
+        <v>569040</v>
       </c>
       <c r="R32" t="n">
-        <v>6380721</v>
+        <v>6380719</v>
       </c>
       <c r="S32" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4021,6 +4009,7 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -4039,10 +4028,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>114799611</v>
+        <v>114799476</v>
       </c>
       <c r="B33" t="n">
-        <v>97535</v>
+        <v>57384</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4051,39 +4040,39 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4091,13 +4080,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>569117</v>
+        <v>569029</v>
       </c>
       <c r="R33" t="n">
-        <v>6380691</v>
+        <v>6380721</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4135,7 +4124,6 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4154,7 +4142,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>114799596</v>
+        <v>114799611</v>
       </c>
       <c r="B34" t="n">
         <v>97535</v>
@@ -4189,7 +4177,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -4206,10 +4194,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>569109</v>
+        <v>569117</v>
       </c>
       <c r="R34" t="n">
-        <v>6380682</v>
+        <v>6380691</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4269,7 +4257,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>114799704</v>
+        <v>114799596</v>
       </c>
       <c r="B35" t="n">
         <v>97535</v>
@@ -4304,7 +4292,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -4321,10 +4309,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>568645</v>
+        <v>569109</v>
       </c>
       <c r="R35" t="n">
-        <v>6380578</v>
+        <v>6380682</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4384,7 +4372,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>114799660</v>
+        <v>114799704</v>
       </c>
       <c r="B36" t="n">
         <v>97535</v>
@@ -4419,7 +4407,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -4436,10 +4424,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>569155</v>
+        <v>568645</v>
       </c>
       <c r="R36" t="n">
-        <v>6380762</v>
+        <v>6380578</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4499,7 +4487,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>114799627</v>
+        <v>114799660</v>
       </c>
       <c r="B37" t="n">
         <v>97535</v>
@@ -4551,10 +4539,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>569112</v>
+        <v>569155</v>
       </c>
       <c r="R37" t="n">
-        <v>6380686</v>
+        <v>6380762</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4614,7 +4602,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>114799410</v>
+        <v>114799627</v>
       </c>
       <c r="B38" t="n">
         <v>97535</v>
@@ -4649,7 +4637,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -4666,10 +4654,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>568959</v>
+        <v>569112</v>
       </c>
       <c r="R38" t="n">
-        <v>6380594</v>
+        <v>6380686</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4729,7 +4717,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>114799529</v>
+        <v>114799410</v>
       </c>
       <c r="B39" t="n">
         <v>97535</v>
@@ -4764,7 +4752,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -4781,10 +4769,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>569144</v>
+        <v>568959</v>
       </c>
       <c r="R39" t="n">
-        <v>6380753</v>
+        <v>6380594</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4844,10 +4832,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>114799722</v>
+        <v>114799529</v>
       </c>
       <c r="B40" t="n">
-        <v>57251</v>
+        <v>97535</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4856,35 +4844,39 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -4892,10 +4884,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>568601</v>
+        <v>569144</v>
       </c>
       <c r="R40" t="n">
-        <v>6380587</v>
+        <v>6380753</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4936,6 +4928,7 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -4954,10 +4947,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>114799683</v>
+        <v>114799722</v>
       </c>
       <c r="B41" t="n">
-        <v>57384</v>
+        <v>57251</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4970,33 +4963,29 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr"/>
       <c r="M41" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N41" t="inlineStr"/>
@@ -5006,13 +4995,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>568842</v>
+        <v>568601</v>
       </c>
       <c r="R41" t="n">
-        <v>6380500</v>
+        <v>6380587</v>
       </c>
       <c r="S41" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5068,10 +5057,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>114799582</v>
+        <v>114799683</v>
       </c>
       <c r="B42" t="n">
-        <v>97535</v>
+        <v>57384</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5080,39 +5069,39 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
@@ -5120,13 +5109,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>569082</v>
+        <v>568842</v>
       </c>
       <c r="R42" t="n">
-        <v>6380654</v>
+        <v>6380500</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5164,7 +5153,6 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -5183,7 +5171,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>114799539</v>
+        <v>114799582</v>
       </c>
       <c r="B43" t="n">
         <v>97535</v>
@@ -5218,7 +5206,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -5235,10 +5223,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>569136</v>
+        <v>569082</v>
       </c>
       <c r="R43" t="n">
-        <v>6380752</v>
+        <v>6380654</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5298,7 +5286,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>114799755</v>
+        <v>114799539</v>
       </c>
       <c r="B44" t="n">
         <v>97535</v>
@@ -5333,7 +5321,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -5350,10 +5338,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>568732</v>
+        <v>569136</v>
       </c>
       <c r="R44" t="n">
-        <v>6380593</v>
+        <v>6380752</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5413,7 +5401,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>114799466</v>
+        <v>114799755</v>
       </c>
       <c r="B45" t="n">
         <v>97535</v>
@@ -5448,7 +5436,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -5465,10 +5453,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>568997</v>
+        <v>568732</v>
       </c>
       <c r="R45" t="n">
-        <v>6380645</v>
+        <v>6380593</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5525,6 +5513,343 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>114799466</v>
+      </c>
+      <c r="B46" t="n">
+        <v>97535</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>A 2837, Tunasjön, Sm</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>568997</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6380645</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Tuna</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2024-02-22</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2024-02-22</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF46" t="inlineStr"/>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>114799787</v>
+      </c>
+      <c r="B47" t="n">
+        <v>57597</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>A 2837, Tunasjön, Sm</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>568897</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6380627</v>
+      </c>
+      <c r="S47" t="n">
+        <v>150</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Tuna</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2024-02-22</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2024-02-22</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Första sången i år!</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>114786708</v>
+      </c>
+      <c r="B48" t="n">
+        <v>57597</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Mörtviken, Sm</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>568934</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6380666</v>
+      </c>
+      <c r="S48" t="n">
+        <v>25</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Tuna</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2024-02-22</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2024-02-22</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
